--- a/public/gabarit-import-apprenants.xlsx
+++ b/public/gabarit-import-apprenants.xlsx
@@ -11,145 +11,145 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="1" max="1" width="29" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="24" customWidth="1"/>
-    <col min="13" max="13" width="23" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="13" max="13" width="21" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
     <col min="15" max="15" width="19" customWidth="1"/>
-    <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="22" customWidth="1"/>
-    <col min="18" max="18" width="17" customWidth="1"/>
-    <col min="19" max="19" width="20" customWidth="1"/>
-    <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="24" customWidth="1"/>
-    <col min="22" max="22" width="23" customWidth="1"/>
-    <col min="23" max="23" width="23" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
+    <col min="17" max="17" width="23" customWidth="1"/>
+    <col min="18" max="18" width="22" customWidth="1"/>
+    <col min="19" max="19" width="22" customWidth="1"/>
+    <col min="20" max="20" width="27" customWidth="1"/>
+    <col min="21" max="21" width="30" customWidth="1"/>
+    <col min="22" max="22" width="32" customWidth="1"/>
+    <col min="23" max="23" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 NOM</t>
+          <t xml:space="preserve">Tuteur 1 NOM (obligatoire)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Prénom</t>
+          <t xml:space="preserve">Tuteur 1 Prénom (obligatoire)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Email</t>
+          <t xml:space="preserve">Tuteur 1 Email (obligatoire)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enfant NOM</t>
+          <t xml:space="preserve">Tuteur 1 Téléphone</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enfant Prénom</t>
+          <t xml:space="preserve">Tuteur 1 Lien</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date de naissance</t>
+          <t xml:space="preserve">Tuteur 1 Adresse</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genre</t>
+          <t xml:space="preserve">Tuteur 1 Ville</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Téléphone</t>
+          <t xml:space="preserve">Tuteur 1 Code postal</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Lien</t>
+          <t xml:space="preserve">Tuteur 1 Profession</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Adresse</t>
+          <t xml:space="preserve">Tuteur 2 NOM</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Ville</t>
+          <t xml:space="preserve">Tuteur 2 Prénom</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Code postal</t>
+          <t xml:space="preserve">Tuteur 2 Email</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Profession</t>
+          <t xml:space="preserve">Tuteur 2 Téléphone</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 NOM</t>
+          <t xml:space="preserve">Tuteur 2 Lien</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Prénom</t>
+          <t xml:space="preserve">Tuteur 2 Adresse</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Email</t>
+          <t xml:space="preserve">Tuteur 2 Ville</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Téléphone</t>
+          <t xml:space="preserve">Tuteur 2 Code postal</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Lien</t>
+          <t xml:space="preserve">Tuteur 2 Profession</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Adresse</t>
+          <t xml:space="preserve">Situation familiale</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Ville</t>
+          <t xml:space="preserve">Enfant NOM (obligatoire)</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Code postal</t>
+          <t xml:space="preserve">Enfant Prénom (obligatoire)</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Profession</t>
+          <t xml:space="preserve">Date de naissance (obligatoire)</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Situation familiale</t>
+          <t xml:space="preserve">Genre (obligatoire)</t>
         </is>
       </c>
     </row>
@@ -160,7 +160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="70" customWidth="1"/>
   </cols>
@@ -185,7 +185,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 NOM</t>
+          <t xml:space="preserve">Tuteur 1 NOM (obligatoire)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -202,7 +202,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Prénom</t>
+          <t xml:space="preserve">Tuteur 1 Prénom (obligatoire)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -219,7 +219,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Email</t>
+          <t xml:space="preserve">Tuteur 1 Email (obligatoire)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -236,75 +236,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enfant NOM</t>
+          <t xml:space="preserve">Tuteur 1 Téléphone</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oui</t>
+          <t xml:space="preserve">Non</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texte — mis en MAJUSCULES à l’import</t>
+          <t xml:space="preserve">06 12 34 56 78 · +213 6 61 23 45 67 · indicatif reconnu</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enfant Prénom</t>
+          <t xml:space="preserve">Tuteur 1 Lien</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oui</t>
+          <t xml:space="preserve">Non</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texte — première lettre mise en capitale</t>
+          <t xml:space="preserve">Pere, Papa, Mere, Maman, Tuteur legal, Tuteur, Autre</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date de naissance</t>
+          <t xml:space="preserve">Tuteur 1 Adresse</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oui</t>
+          <t xml:space="preserve">Non</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">JJ/MM/AAAA (ou une vraie date du tableur)</t>
+          <t xml:space="preserve">Texte libre</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genre</t>
+          <t xml:space="preserve">Tuteur 1 Ville</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oui</t>
+          <t xml:space="preserve">Non</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masculin, M, Garcon, H, Homme, Feminin, F, Fille, Femme, Non specifie, NS</t>
+          <t xml:space="preserve">Texte libre</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Téléphone</t>
+          <t xml:space="preserve">Tuteur 1 Code postal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -314,14 +314,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">06 12 34 56 78 · +213 6 61 23 45 67 · indicatif reconnu</t>
+          <t xml:space="preserve">5 chiffres</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Lien</t>
+          <t xml:space="preserve">Tuteur 1 Profession</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -331,14 +331,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pere, Papa, Mere, Maman, Tuteur legal, Tuteur, Autre</t>
+          <t xml:space="preserve">Texte libre</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Adresse</t>
+          <t xml:space="preserve">Tuteur 2 NOM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -348,14 +348,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texte libre</t>
+          <t xml:space="preserve">Texte — mis en MAJUSCULES à l’import</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Ville</t>
+          <t xml:space="preserve">Tuteur 2 Prénom</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -365,14 +365,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texte libre</t>
+          <t xml:space="preserve">Texte — première lettre mise en capitale</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Code postal</t>
+          <t xml:space="preserve">Tuteur 2 Email</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -382,14 +382,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 chiffres</t>
+          <t xml:space="preserve">adresse@exemple.fr</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 1 Profession</t>
+          <t xml:space="preserve">Tuteur 2 Téléphone</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -399,14 +399,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texte libre</t>
+          <t xml:space="preserve">06 12 34 56 78 · +213 6 61 23 45 67 · indicatif reconnu</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 NOM</t>
+          <t xml:space="preserve">Tuteur 2 Lien</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -416,14 +416,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texte — mis en MAJUSCULES à l’import</t>
+          <t xml:space="preserve">Pere, Papa, Mere, Maman, Tuteur legal, Tuteur, Autre</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Prénom</t>
+          <t xml:space="preserve">Tuteur 2 Adresse</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -433,14 +433,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texte — première lettre mise en capitale</t>
+          <t xml:space="preserve">Texte libre</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Email</t>
+          <t xml:space="preserve">Tuteur 2 Ville</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -450,14 +450,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">adresse@exemple.fr</t>
+          <t xml:space="preserve">Texte libre</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Téléphone</t>
+          <t xml:space="preserve">Tuteur 2 Code postal</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -467,14 +467,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">06 12 34 56 78 · +213 6 61 23 45 67 · indicatif reconnu</t>
+          <t xml:space="preserve">5 chiffres</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Lien</t>
+          <t xml:space="preserve">Tuteur 2 Profession</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -484,14 +484,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pere, Papa, Mere, Maman, Tuteur legal, Tuteur, Autre</t>
+          <t xml:space="preserve">Texte libre</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Adresse</t>
+          <t xml:space="preserve">Situation familiale</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -501,75 +501,75 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texte libre</t>
+          <t xml:space="preserve">Maries, Marie, Pacses, Pacse, Union libre, Concubinage, Separes, Separe, Divorces, Divorce, Veuf, Veuve, Veuf/Veuve, Monoparental, Famille monoparentale</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Ville</t>
+          <t xml:space="preserve">Enfant NOM (obligatoire)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non</t>
+          <t xml:space="preserve">Oui</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texte libre</t>
+          <t xml:space="preserve">Texte — mis en MAJUSCULES à l’import</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Code postal</t>
+          <t xml:space="preserve">Enfant Prénom (obligatoire)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non</t>
+          <t xml:space="preserve">Oui</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 chiffres</t>
+          <t xml:space="preserve">Texte — première lettre mise en capitale</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuteur 2 Profession</t>
+          <t xml:space="preserve">Date de naissance (obligatoire)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non</t>
+          <t xml:space="preserve">Oui</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texte libre</t>
+          <t xml:space="preserve">JJ/MM/AAAA (ou une vraie date du tableur)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Situation familiale</t>
+          <t xml:space="preserve">Genre (obligatoire)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non</t>
+          <t xml:space="preserve">Oui</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maries, Marie, Pacses, Pacse, Union libre, Concubinage, Separes, Separe, Divorces, Divorce, Veuf, Veuve, Veuf/Veuve, Monoparental, Famille monoparentale</t>
+          <t xml:space="preserve">Masculin, M, Garcon, H, Homme, Feminin, F, Fille, Femme, Non specifie, NS</t>
         </is>
       </c>
     </row>

--- a/public/gabarit-import-apprenants.xlsx
+++ b/public/gabarit-import-apprenants.xlsx
@@ -154,6 +154,20 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur non acceptée" error="Choisissez une valeur dans la liste." sqref="E2:E1000">
+      <formula1>"Père,Mère,Tuteur légal,Autre"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur non acceptée" error="Choisissez une valeur dans la liste." sqref="N2:N1000">
+      <formula1>"Père,Mère,Tuteur légal,Autre"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur non acceptée" error="Choisissez une valeur dans la liste." sqref="S2:S1000">
+      <formula1>"Mariés,Pacsés,Union libre,Séparés,Divorcés,Veuf / Veuve,Famille monoparentale"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valeur non acceptée" error="Choisissez une valeur dans la liste." sqref="W2:W1000">
+      <formula1>"Masculin,Féminin,Non spécifié"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
 
@@ -263,7 +277,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pere, Papa, Mere, Maman, Tuteur legal, Tuteur, Autre</t>
+          <t xml:space="preserve">Père, Pere, Papa, Mère, Mere, Maman, Tuteur légal, Tuteur legal, Tuteur, Autre</t>
         </is>
       </c>
     </row>
@@ -416,7 +430,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pere, Papa, Mere, Maman, Tuteur legal, Tuteur, Autre</t>
+          <t xml:space="preserve">Père, Pere, Papa, Mère, Mere, Maman, Tuteur légal, Tuteur legal, Tuteur, Autre</t>
         </is>
       </c>
     </row>
@@ -501,7 +515,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maries, Marie, Pacses, Pacse, Union libre, Concubinage, Separes, Separe, Divorces, Divorce, Veuf, Veuve, Veuf/Veuve, Monoparental, Famille monoparentale</t>
+          <t xml:space="preserve">Mariés, Marie, Maries, Pacsés, Pacse, Pacses, Union libre, Concubinage, Séparés, Separe, Separes, Divorcés, Divorce, Divorces, Veuf / Veuve, Veuf, Veuve, Famille monoparentale, Monoparental</t>
         </is>
       </c>
     </row>
@@ -569,7 +583,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masculin, M, Garcon, H, Homme, Feminin, F, Fille, Femme, Non specifie, NS</t>
+          <t xml:space="preserve">Masculin, M, Garçon, Garcon, H, Homme, Féminin, Feminin, F, Fille, Femme, Non spécifié, Non specifie, NS</t>
         </is>
       </c>
     </row>

--- a/public/gabarit-import-apprenants.xlsx
+++ b/public/gabarit-import-apprenants.xlsx
@@ -8,26 +8,67 @@
 </workbook>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  </cellXfs>
+  <!-- Facultatif au schema, mais Excel le reclame en pratique : sans lui il
+     signale un classeur « a reparer », ce qui serait pire que le probleme
+     qu'on corrige. -->
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="31" customWidth="1"/>
-    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1" style="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1" style="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="21" customWidth="1"/>
+    <col min="13" max="13" width="21" customWidth="1" style="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
     <col min="15" max="15" width="19" customWidth="1"/>
     <col min="16" max="16" width="17" customWidth="1"/>
-    <col min="17" max="17" width="23" customWidth="1"/>
+    <col min="17" max="17" width="23" customWidth="1" style="1"/>
     <col min="18" max="18" width="22" customWidth="1"/>
     <col min="19" max="19" width="22" customWidth="1"/>
     <col min="20" max="20" width="27" customWidth="1"/>
